--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_valparaiso.xlsx
@@ -75,12 +75,12 @@
     <t xml:space="preserve">Zapallar</t>
   </si>
   <si>
+    <t xml:space="preserve">Hijuelas</t>
+  </si>
+  <si>
     <t xml:space="preserve">Quillota</t>
   </si>
   <si>
-    <t xml:space="preserve">Hijuelas</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cartagena</t>
   </si>
   <si>
@@ -141,12 +141,12 @@
     <t xml:space="preserve">Juan Fernández</t>
   </si>
   <si>
+    <t xml:space="preserve">Calera</t>
+  </si>
+  <si>
     <t xml:space="preserve">Llaillay</t>
   </si>
   <si>
-    <t xml:space="preserve">Calera</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:27</t>
+    <t xml:space="preserve">2026-09-09 23:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -807,7 +807,7 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>5501</v>
+        <v>5503</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2021</v>
@@ -824,7 +824,7 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>5503</v>
+        <v>5501</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2021</v>
@@ -1198,7 +1198,7 @@
         <v>41</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>5703</v>
+        <v>5502</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
@@ -1211,7 +1211,7 @@
         <v>42</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>5502</v>
+        <v>5703</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:24</t>
+    <t xml:space="preserve">2026-09-17 14:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_valparaiso.xlsx
@@ -75,12 +75,12 @@
     <t xml:space="preserve">Zapallar</t>
   </si>
   <si>
+    <t xml:space="preserve">Quillota</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hijuelas</t>
   </si>
   <si>
-    <t xml:space="preserve">Quillota</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cartagena</t>
   </si>
   <si>
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:19</t>
+    <t xml:space="preserve">2026-09-23 12:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -807,7 +807,7 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>5503</v>
+        <v>5501</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2021</v>
@@ -824,7 +824,7 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>5501</v>
+        <v>5503</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2021</v>
@@ -1200,7 +1200,9 @@
       <c r="C38" s="2" t="n">
         <v>5502</v>
       </c>
-      <c r="D38" s="2"/>
+      <c r="D38" s="2" t="n">
+        <v>2021</v>
+      </c>
       <c r="E38" s="2"/>
     </row>
     <row r="39">
@@ -1213,7 +1215,9 @@
       <c r="C39" s="2" t="n">
         <v>5703</v>
       </c>
-      <c r="D39" s="2"/>
+      <c r="D39" s="2" t="n">
+        <v>2021</v>
+      </c>
       <c r="E39" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_valparaiso.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t xml:space="preserve">Región</t>
   </si>
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:47</t>
+    <t xml:space="preserve">2026-10-01 23:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -174,7 +174,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingreso sobre la mediana nacional (%)</t>
+    <t xml:space="preserve">% bajo 50% de la mediana</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
@@ -187,9 +187,6 @@
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% sobre mediana</t>
   </si>
 </sst>
 </file>
@@ -1297,7 +1294,7 @@
         <v>56</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:06</t>
+    <t xml:space="preserve">2026-10-02 11:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 11:20</t>
+    <t xml:space="preserve">2026-10-02 15:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:06</t>
+    <t xml:space="preserve">2026-10-04 09:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:22</t>
+    <t xml:space="preserve">2026-10-05 12:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
